--- a/Antonia/annotation_template_filled.xlsx
+++ b/Antonia/annotation_template_filled.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anton\Desktop\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{762DA56E-8A67-43E9-BA16-4F097114E468}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E5FA4D8-CB5F-4FEF-B368-6EB693C64D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="448">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1326" uniqueCount="450">
   <si>
     <t>post_id</t>
   </si>
@@ -1534,6 +1534,12 @@
   <si>
     <t>negative</t>
   </si>
+  <si>
+    <t>Final_Opinion</t>
+  </si>
+  <si>
+    <t>no_majority</t>
+  </si>
 </sst>
 </file>
 
@@ -1564,7 +1570,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -1587,13 +1593,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1900,13 +1920,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E221"/>
+  <dimension ref="A1:F221"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="62.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1922,8 +1942,11 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F1" s="2" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -1939,8 +1962,11 @@
       <c r="E2" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F2" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -1956,8 +1982,11 @@
       <c r="E3" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F3" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>7</v>
       </c>
@@ -1973,8 +2002,11 @@
       <c r="E4" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F4" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -1990,8 +2022,11 @@
       <c r="E5" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F5" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>9</v>
       </c>
@@ -2007,8 +2042,11 @@
       <c r="E6" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F6" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>10</v>
       </c>
@@ -2024,8 +2062,11 @@
       <c r="E7" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F7" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>11</v>
       </c>
@@ -2041,8 +2082,11 @@
       <c r="E8" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F8" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>12</v>
       </c>
@@ -2058,8 +2102,11 @@
       <c r="E9" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F9" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>13</v>
       </c>
@@ -2075,8 +2122,11 @@
       <c r="E10" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F10" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>14</v>
       </c>
@@ -2092,8 +2142,11 @@
       <c r="E11" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F11" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>15</v>
       </c>
@@ -2109,8 +2162,11 @@
       <c r="E12" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F12" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>16</v>
       </c>
@@ -2126,8 +2182,11 @@
       <c r="E13" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F13" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>17</v>
       </c>
@@ -2143,8 +2202,11 @@
       <c r="E14" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F14" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>18</v>
       </c>
@@ -2160,8 +2222,11 @@
       <c r="E15" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F15" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>19</v>
       </c>
@@ -2177,8 +2242,11 @@
       <c r="E16" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F16" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>20</v>
       </c>
@@ -2194,8 +2262,11 @@
       <c r="E17" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F17" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>21</v>
       </c>
@@ -2211,8 +2282,11 @@
       <c r="E18" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F18" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>22</v>
       </c>
@@ -2228,8 +2302,11 @@
       <c r="E19" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F19" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>23</v>
       </c>
@@ -2245,8 +2322,11 @@
       <c r="E20" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F20" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>24</v>
       </c>
@@ -2262,8 +2342,11 @@
       <c r="E21" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F21" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>25</v>
       </c>
@@ -2279,8 +2362,11 @@
       <c r="E22" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F22" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>26</v>
       </c>
@@ -2296,8 +2382,11 @@
       <c r="E23" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F23" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>27</v>
       </c>
@@ -2313,8 +2402,11 @@
       <c r="E24" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F24" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>28</v>
       </c>
@@ -2330,8 +2422,11 @@
       <c r="E25" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F25" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>29</v>
       </c>
@@ -2347,8 +2442,11 @@
       <c r="E26" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F26" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>30</v>
       </c>
@@ -2364,8 +2462,11 @@
       <c r="E27" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F27" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>31</v>
       </c>
@@ -2381,8 +2482,11 @@
       <c r="E28" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F28" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>32</v>
       </c>
@@ -2398,8 +2502,11 @@
       <c r="E29" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F29" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>33</v>
       </c>
@@ -2415,8 +2522,11 @@
       <c r="E30" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F30" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>34</v>
       </c>
@@ -2432,8 +2542,11 @@
       <c r="E31" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F31" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>35</v>
       </c>
@@ -2449,8 +2562,11 @@
       <c r="E32" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F32" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>36</v>
       </c>
@@ -2466,8 +2582,11 @@
       <c r="E33" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F33" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>37</v>
       </c>
@@ -2483,8 +2602,11 @@
       <c r="E34" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F34" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>38</v>
       </c>
@@ -2500,8 +2622,11 @@
       <c r="E35" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F35" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>39</v>
       </c>
@@ -2517,8 +2642,11 @@
       <c r="E36" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F36" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -2534,8 +2662,11 @@
       <c r="E37" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F37" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>41</v>
       </c>
@@ -2551,8 +2682,11 @@
       <c r="E38" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F38" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>42</v>
       </c>
@@ -2568,8 +2702,11 @@
       <c r="E39" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F39" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>43</v>
       </c>
@@ -2585,8 +2722,11 @@
       <c r="E40" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F40" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -2602,8 +2742,11 @@
       <c r="E41" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F41" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>45</v>
       </c>
@@ -2619,8 +2762,11 @@
       <c r="E42" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F42" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>46</v>
       </c>
@@ -2636,8 +2782,11 @@
       <c r="E43" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F43" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>47</v>
       </c>
@@ -2653,8 +2802,11 @@
       <c r="E44" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F44" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>48</v>
       </c>
@@ -2670,8 +2822,11 @@
       <c r="E45" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F45" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>49</v>
       </c>
@@ -2687,8 +2842,11 @@
       <c r="E46" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F46" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>50</v>
       </c>
@@ -2704,8 +2862,11 @@
       <c r="E47" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F47" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>51</v>
       </c>
@@ -2721,8 +2882,11 @@
       <c r="E48" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F48" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>52</v>
       </c>
@@ -2738,8 +2902,11 @@
       <c r="E49" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F49" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>53</v>
       </c>
@@ -2755,8 +2922,11 @@
       <c r="E50" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F50" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>54</v>
       </c>
@@ -2772,8 +2942,11 @@
       <c r="E51" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F51" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>55</v>
       </c>
@@ -2789,8 +2962,11 @@
       <c r="E52" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F52" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>56</v>
       </c>
@@ -2806,8 +2982,11 @@
       <c r="E53" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F53" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>57</v>
       </c>
@@ -2823,8 +3002,11 @@
       <c r="E54" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F54" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>58</v>
       </c>
@@ -2840,8 +3022,11 @@
       <c r="E55" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F55" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>59</v>
       </c>
@@ -2857,8 +3042,11 @@
       <c r="E56" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F56" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>60</v>
       </c>
@@ -2874,8 +3062,11 @@
       <c r="E57" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F57" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>61</v>
       </c>
@@ -2891,8 +3082,11 @@
       <c r="E58" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F58" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>62</v>
       </c>
@@ -2908,8 +3102,11 @@
       <c r="E59" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F59" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>63</v>
       </c>
@@ -2925,8 +3122,11 @@
       <c r="E60" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F60" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>64</v>
       </c>
@@ -2942,8 +3142,11 @@
       <c r="E61" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F61" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>65</v>
       </c>
@@ -2959,8 +3162,11 @@
       <c r="E62" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F62" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>66</v>
       </c>
@@ -2976,8 +3182,11 @@
       <c r="E63" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F63" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>67</v>
       </c>
@@ -2993,8 +3202,11 @@
       <c r="E64" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F64" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>68</v>
       </c>
@@ -3010,8 +3222,11 @@
       <c r="E65" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F65" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>69</v>
       </c>
@@ -3027,8 +3242,11 @@
       <c r="E66" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F66" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>70</v>
       </c>
@@ -3044,8 +3262,11 @@
       <c r="E67" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F67" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>71</v>
       </c>
@@ -3061,8 +3282,11 @@
       <c r="E68" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F68" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>72</v>
       </c>
@@ -3078,8 +3302,11 @@
       <c r="E69" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F69" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>73</v>
       </c>
@@ -3095,8 +3322,11 @@
       <c r="E70" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F70" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>74</v>
       </c>
@@ -3112,8 +3342,11 @@
       <c r="E71" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F71" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>75</v>
       </c>
@@ -3129,8 +3362,11 @@
       <c r="E72" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F72" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>76</v>
       </c>
@@ -3146,8 +3382,11 @@
       <c r="E73" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F73" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>77</v>
       </c>
@@ -3163,8 +3402,11 @@
       <c r="E74" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F74" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>78</v>
       </c>
@@ -3180,8 +3422,11 @@
       <c r="E75" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F75" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>79</v>
       </c>
@@ -3197,8 +3442,11 @@
       <c r="E76" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F76" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>80</v>
       </c>
@@ -3214,8 +3462,11 @@
       <c r="E77" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F77" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>81</v>
       </c>
@@ -3231,8 +3482,11 @@
       <c r="E78" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F78" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>82</v>
       </c>
@@ -3248,8 +3502,11 @@
       <c r="E79" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F79" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>83</v>
       </c>
@@ -3265,8 +3522,11 @@
       <c r="E80" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F80" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>84</v>
       </c>
@@ -3282,8 +3542,11 @@
       <c r="E81" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F81" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>85</v>
       </c>
@@ -3299,8 +3562,11 @@
       <c r="E82" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F82" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>86</v>
       </c>
@@ -3316,8 +3582,11 @@
       <c r="E83" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F83" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>87</v>
       </c>
@@ -3333,8 +3602,11 @@
       <c r="E84" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F84" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>88</v>
       </c>
@@ -3350,8 +3622,11 @@
       <c r="E85" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F85" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>89</v>
       </c>
@@ -3367,8 +3642,11 @@
       <c r="E86" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F86" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>90</v>
       </c>
@@ -3384,8 +3662,11 @@
       <c r="E87" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F87" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>91</v>
       </c>
@@ -3401,8 +3682,11 @@
       <c r="E88" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F88" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>92</v>
       </c>
@@ -3418,8 +3702,11 @@
       <c r="E89" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F89" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>93</v>
       </c>
@@ -3435,8 +3722,11 @@
       <c r="E90" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F90" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>94</v>
       </c>
@@ -3452,8 +3742,11 @@
       <c r="E91" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F91" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>95</v>
       </c>
@@ -3469,8 +3762,11 @@
       <c r="E92" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F92" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>96</v>
       </c>
@@ -3486,8 +3782,11 @@
       <c r="E93" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F93" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>97</v>
       </c>
@@ -3503,8 +3802,11 @@
       <c r="E94" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F94" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>98</v>
       </c>
@@ -3520,8 +3822,11 @@
       <c r="E95" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F95" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>99</v>
       </c>
@@ -3537,8 +3842,11 @@
       <c r="E96" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F96" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>100</v>
       </c>
@@ -3554,8 +3862,11 @@
       <c r="E97" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F97" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>101</v>
       </c>
@@ -3571,8 +3882,11 @@
       <c r="E98" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F98" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>102</v>
       </c>
@@ -3588,8 +3902,11 @@
       <c r="E99" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F99" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>103</v>
       </c>
@@ -3605,8 +3922,11 @@
       <c r="E100" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="101" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F100" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>104</v>
       </c>
@@ -3622,8 +3942,11 @@
       <c r="E101" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="102" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F101" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>105</v>
       </c>
@@ -3639,8 +3962,11 @@
       <c r="E102" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="103" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F102" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>106</v>
       </c>
@@ -3656,8 +3982,11 @@
       <c r="E103" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F103" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>107</v>
       </c>
@@ -3673,8 +4002,11 @@
       <c r="E104" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F104" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>108</v>
       </c>
@@ -3690,8 +4022,11 @@
       <c r="E105" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="106" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F105" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>109</v>
       </c>
@@ -3707,8 +4042,11 @@
       <c r="E106" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="107" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F106" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>110</v>
       </c>
@@ -3724,8 +4062,11 @@
       <c r="E107" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="108" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F107" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>111</v>
       </c>
@@ -3741,8 +4082,11 @@
       <c r="E108" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F108" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>112</v>
       </c>
@@ -3758,8 +4102,11 @@
       <c r="E109" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="110" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F109" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>113</v>
       </c>
@@ -3775,8 +4122,11 @@
       <c r="E110" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="111" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F110" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>114</v>
       </c>
@@ -3792,8 +4142,11 @@
       <c r="E111" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="112" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F111" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>115</v>
       </c>
@@ -3809,8 +4162,11 @@
       <c r="E112" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F112" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>116</v>
       </c>
@@ -3826,8 +4182,11 @@
       <c r="E113" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F113" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>117</v>
       </c>
@@ -3843,8 +4202,11 @@
       <c r="E114" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F114" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>118</v>
       </c>
@@ -3860,8 +4222,11 @@
       <c r="E115" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F115" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>119</v>
       </c>
@@ -3877,8 +4242,11 @@
       <c r="E116" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F116" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>120</v>
       </c>
@@ -3894,8 +4262,11 @@
       <c r="E117" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F117" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="118" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>121</v>
       </c>
@@ -3911,8 +4282,11 @@
       <c r="E118" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F118" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>122</v>
       </c>
@@ -3928,8 +4302,11 @@
       <c r="E119" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F119" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>123</v>
       </c>
@@ -3945,8 +4322,11 @@
       <c r="E120" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F120" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>124</v>
       </c>
@@ -3962,8 +4342,11 @@
       <c r="E121" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F121" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>125</v>
       </c>
@@ -3979,8 +4362,11 @@
       <c r="E122" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F122" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>126</v>
       </c>
@@ -3996,8 +4382,11 @@
       <c r="E123" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F123" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>127</v>
       </c>
@@ -4013,8 +4402,11 @@
       <c r="E124" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F124" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>128</v>
       </c>
@@ -4030,8 +4422,11 @@
       <c r="E125" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F125" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>129</v>
       </c>
@@ -4047,8 +4442,11 @@
       <c r="E126" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F126" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>130</v>
       </c>
@@ -4064,8 +4462,11 @@
       <c r="E127" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F127" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>131</v>
       </c>
@@ -4081,8 +4482,11 @@
       <c r="E128" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F128" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>132</v>
       </c>
@@ -4098,8 +4502,11 @@
       <c r="E129" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F129" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>133</v>
       </c>
@@ -4115,8 +4522,11 @@
       <c r="E130" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F130" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>134</v>
       </c>
@@ -4132,8 +4542,11 @@
       <c r="E131" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F131" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>135</v>
       </c>
@@ -4149,8 +4562,11 @@
       <c r="E132" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F132" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>136</v>
       </c>
@@ -4166,8 +4582,11 @@
       <c r="E133" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F133" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>137</v>
       </c>
@@ -4183,8 +4602,11 @@
       <c r="E134" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F134" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>138</v>
       </c>
@@ -4200,8 +4622,11 @@
       <c r="E135" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F135" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>139</v>
       </c>
@@ -4217,8 +4642,11 @@
       <c r="E136" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F136" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>140</v>
       </c>
@@ -4234,8 +4662,11 @@
       <c r="E137" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F137" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>141</v>
       </c>
@@ -4251,8 +4682,11 @@
       <c r="E138" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F138" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>142</v>
       </c>
@@ -4268,8 +4702,11 @@
       <c r="E139" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F139" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>143</v>
       </c>
@@ -4285,8 +4722,11 @@
       <c r="E140" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F140" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>144</v>
       </c>
@@ -4302,8 +4742,11 @@
       <c r="E141" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F141" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>145</v>
       </c>
@@ -4319,8 +4762,11 @@
       <c r="E142" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F142" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>146</v>
       </c>
@@ -4336,8 +4782,11 @@
       <c r="E143" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F143" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>147</v>
       </c>
@@ -4353,8 +4802,11 @@
       <c r="E144" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F144" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>148</v>
       </c>
@@ -4370,8 +4822,11 @@
       <c r="E145" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F145" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>149</v>
       </c>
@@ -4387,8 +4842,11 @@
       <c r="E146" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F146" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>150</v>
       </c>
@@ -4404,8 +4862,11 @@
       <c r="E147" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F147" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>151</v>
       </c>
@@ -4421,8 +4882,11 @@
       <c r="E148" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F148" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>152</v>
       </c>
@@ -4438,8 +4902,11 @@
       <c r="E149" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F149" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="150" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>153</v>
       </c>
@@ -4455,8 +4922,11 @@
       <c r="E150" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F150" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="151" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>154</v>
       </c>
@@ -4472,8 +4942,11 @@
       <c r="E151" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F151" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="152" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>155</v>
       </c>
@@ -4489,8 +4962,11 @@
       <c r="E152" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F152" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="153" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>156</v>
       </c>
@@ -4506,8 +4982,11 @@
       <c r="E153" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F153" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="154" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>157</v>
       </c>
@@ -4523,8 +5002,11 @@
       <c r="E154" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F154" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="155" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>158</v>
       </c>
@@ -4540,8 +5022,11 @@
       <c r="E155" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F155" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="156" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>159</v>
       </c>
@@ -4557,8 +5042,11 @@
       <c r="E156" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F156" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="157" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>160</v>
       </c>
@@ -4574,8 +5062,11 @@
       <c r="E157" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F157" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="158" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>161</v>
       </c>
@@ -4591,8 +5082,11 @@
       <c r="E158" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F158" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="159" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>162</v>
       </c>
@@ -4608,8 +5102,11 @@
       <c r="E159" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F159" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="160" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>163</v>
       </c>
@@ -4625,8 +5122,11 @@
       <c r="E160" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F160" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="161" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>164</v>
       </c>
@@ -4642,8 +5142,11 @@
       <c r="E161" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F161" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="162" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>165</v>
       </c>
@@ -4659,8 +5162,11 @@
       <c r="E162" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F162" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="163" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>166</v>
       </c>
@@ -4676,8 +5182,11 @@
       <c r="E163" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F163" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="164" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>167</v>
       </c>
@@ -4693,8 +5202,11 @@
       <c r="E164" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F164" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="165" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>168</v>
       </c>
@@ -4710,8 +5222,11 @@
       <c r="E165" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F165" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="166" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>169</v>
       </c>
@@ -4727,8 +5242,11 @@
       <c r="E166" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F166" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="167" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>170</v>
       </c>
@@ -4744,8 +5262,11 @@
       <c r="E167" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F167" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="168" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>171</v>
       </c>
@@ -4761,8 +5282,11 @@
       <c r="E168" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F168" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="169" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>172</v>
       </c>
@@ -4778,8 +5302,11 @@
       <c r="E169" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F169" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="170" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>173</v>
       </c>
@@ -4795,8 +5322,11 @@
       <c r="E170" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F170" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="171" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>174</v>
       </c>
@@ -4812,8 +5342,11 @@
       <c r="E171" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F171" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="172" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>175</v>
       </c>
@@ -4829,8 +5362,11 @@
       <c r="E172" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F172" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="173" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>176</v>
       </c>
@@ -4846,8 +5382,11 @@
       <c r="E173" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F173" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="174" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>177</v>
       </c>
@@ -4863,8 +5402,11 @@
       <c r="E174" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F174" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="175" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>178</v>
       </c>
@@ -4880,8 +5422,11 @@
       <c r="E175" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F175" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="176" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>179</v>
       </c>
@@ -4897,8 +5442,11 @@
       <c r="E176" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F176" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="177" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>180</v>
       </c>
@@ -4914,8 +5462,11 @@
       <c r="E177" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F177" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="178" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>181</v>
       </c>
@@ -4931,8 +5482,11 @@
       <c r="E178" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F178" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="179" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>182</v>
       </c>
@@ -4948,8 +5502,11 @@
       <c r="E179" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F179" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="180" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>183</v>
       </c>
@@ -4965,8 +5522,11 @@
       <c r="E180" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F180" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="181" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>184</v>
       </c>
@@ -4982,8 +5542,11 @@
       <c r="E181" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F181" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="182" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>185</v>
       </c>
@@ -4999,8 +5562,11 @@
       <c r="E182" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F182" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="183" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>186</v>
       </c>
@@ -5016,8 +5582,11 @@
       <c r="E183" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F183" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="184" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>187</v>
       </c>
@@ -5033,8 +5602,11 @@
       <c r="E184" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F184" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="185" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>188</v>
       </c>
@@ -5050,8 +5622,11 @@
       <c r="E185" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F185" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="186" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>189</v>
       </c>
@@ -5067,8 +5642,11 @@
       <c r="E186" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F186" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="187" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>190</v>
       </c>
@@ -5084,8 +5662,11 @@
       <c r="E187" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F187" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="188" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>191</v>
       </c>
@@ -5101,8 +5682,11 @@
       <c r="E188" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F188" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="189" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>192</v>
       </c>
@@ -5118,8 +5702,11 @@
       <c r="E189" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F189" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="190" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>193</v>
       </c>
@@ -5135,8 +5722,11 @@
       <c r="E190" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F190" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="191" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>194</v>
       </c>
@@ -5152,8 +5742,11 @@
       <c r="E191" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F191" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="192" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>195</v>
       </c>
@@ -5169,8 +5762,11 @@
       <c r="E192" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F192" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="193" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>196</v>
       </c>
@@ -5186,8 +5782,11 @@
       <c r="E193" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F193" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="194" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>197</v>
       </c>
@@ -5203,8 +5802,11 @@
       <c r="E194" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F194" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="195" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>198</v>
       </c>
@@ -5220,8 +5822,11 @@
       <c r="E195" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F195" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="196" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>199</v>
       </c>
@@ -5237,8 +5842,11 @@
       <c r="E196" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F196" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="197" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>200</v>
       </c>
@@ -5254,8 +5862,11 @@
       <c r="E197" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F197" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="198" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>201</v>
       </c>
@@ -5271,8 +5882,11 @@
       <c r="E198" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F198" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="199" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>202</v>
       </c>
@@ -5288,8 +5902,11 @@
       <c r="E199" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F199" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="200" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>203</v>
       </c>
@@ -5305,8 +5922,11 @@
       <c r="E200" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F200" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="201" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>204</v>
       </c>
@@ -5322,8 +5942,11 @@
       <c r="E201" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F201" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="202" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>205</v>
       </c>
@@ -5339,8 +5962,11 @@
       <c r="E202" t="s">
         <v>447</v>
       </c>
-    </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F202" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="203" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>206</v>
       </c>
@@ -5356,8 +5982,11 @@
       <c r="E203" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F203" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="204" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>207</v>
       </c>
@@ -5373,8 +6002,11 @@
       <c r="E204" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F204" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="205" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>208</v>
       </c>
@@ -5390,8 +6022,11 @@
       <c r="E205" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F205" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="206" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>209</v>
       </c>
@@ -5407,8 +6042,11 @@
       <c r="E206" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F206" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="207" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>210</v>
       </c>
@@ -5424,8 +6062,11 @@
       <c r="E207" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F207" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="208" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>211</v>
       </c>
@@ -5441,8 +6082,11 @@
       <c r="E208" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="209" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F208" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="209" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>212</v>
       </c>
@@ -5458,8 +6102,11 @@
       <c r="E209" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="210" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F209" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="210" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>213</v>
       </c>
@@ -5475,8 +6122,11 @@
       <c r="E210" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="211" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F210" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="211" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>214</v>
       </c>
@@ -5492,8 +6142,11 @@
       <c r="E211" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="212" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F211" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>215</v>
       </c>
@@ -5509,8 +6162,11 @@
       <c r="E212" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="213" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F212" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="213" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>216</v>
       </c>
@@ -5526,8 +6182,11 @@
       <c r="E213" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="214" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F213" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>217</v>
       </c>
@@ -5543,8 +6202,11 @@
       <c r="E214" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="215" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F214" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>218</v>
       </c>
@@ -5560,8 +6222,11 @@
       <c r="E215" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="216" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F215" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="216" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>219</v>
       </c>
@@ -5577,8 +6242,11 @@
       <c r="E216" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="217" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F216" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="217" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>220</v>
       </c>
@@ -5594,8 +6262,11 @@
       <c r="E217" t="s">
         <v>445</v>
       </c>
-    </row>
-    <row r="218" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F217" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="218" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>221</v>
       </c>
@@ -5611,8 +6282,11 @@
       <c r="E218" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="219" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F218" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="219" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>222</v>
       </c>
@@ -5628,8 +6302,11 @@
       <c r="E219" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="220" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F219" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="220" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>223</v>
       </c>
@@ -5645,8 +6322,11 @@
       <c r="E220" t="s">
         <v>446</v>
       </c>
-    </row>
-    <row r="221" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="F220" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="221" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>224</v>
       </c>
@@ -5661,6 +6341,9 @@
       </c>
       <c r="E221" t="s">
         <v>446</v>
+      </c>
+      <c r="F221" t="s">
+        <v>447</v>
       </c>
     </row>
   </sheetData>
